--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_40.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2387262.71740193</v>
+        <v>2380353.246291293</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9774782.687313249</v>
+        <v>9774782.687313253</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9774782.687313249</v>
+        <v>9774782.687313253</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138604.3777869983</v>
+        <v>138604.3777869852</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138604.3777869983</v>
+        <v>138604.3777869852</v>
       </c>
     </row>
     <row r="11">
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>16.23472619600334</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>66.5639999646113</v>
+        <v>93.30273619610615</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>120.6316114025499</v>
+        <v>119.040440756494</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -854,7 +854,7 @@
         <v>240.445564079015</v>
       </c>
       <c r="P4" t="n">
-        <v>285.8567266822216</v>
+        <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
         <v>325.839266425598</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>199.8180013219744</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>192.3498461705186</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1447,7 +1447,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1510,10 +1510,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="13">
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1693,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
         <v>69.86273944538755</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>73.77767497096173</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U18" t="n">
         <v>50.21035976018675</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2145,7 +2145,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>161.3174326828064</v>
+        <v>165.2828240682209</v>
       </c>
     </row>
     <row r="21">
@@ -2158,10 +2158,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09991244551929</v>
+        <v>81.10557774904923</v>
       </c>
       <c r="D21" t="n">
-        <v>70.00566530352997</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -2334,7 +2334,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S24" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U24" t="n">
         <v>50.21035976018675</v>
@@ -2565,7 +2565,7 @@
         <v>86.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>80.25316367243062</v>
+        <v>85.75737228701621</v>
       </c>
       <c r="H26" t="n">
         <v>90.00965870352741</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>176.8481678023229</v>
+        <v>171.3439591877485</v>
       </c>
       <c r="T26" t="n">
         <v>268.6755817285639</v>
@@ -2805,7 +2805,7 @@
         <v>85.75737228701621</v>
       </c>
       <c r="H29" t="n">
-        <v>84.50545008899992</v>
+        <v>84.50545008905755</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>229.2737972923793</v>
+        <v>229.2737972923447</v>
       </c>
       <c r="S30" t="n">
         <v>148.5639999646113</v>
@@ -2978,22 +2978,22 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>10.97732208981999</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>322.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>369.4478973282775</v>
+        <v>225.0081667086313</v>
       </c>
       <c r="Q31" t="n">
         <v>407.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>85.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>84.505450088945</v>
+        <v>90.00965870352741</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>274.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>193.3174326828064</v>
+        <v>187.8132240682209</v>
       </c>
     </row>
     <row r="33">
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>229.2737972923793</v>
+        <v>229.2737972923581</v>
       </c>
       <c r="S33" t="n">
         <v>148.5639999646113</v>
@@ -3215,22 +3215,22 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>322.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>369.4478973282775</v>
+        <v>225.0081667086313</v>
       </c>
       <c r="Q34" t="n">
-        <v>216.1849771128682</v>
+        <v>407.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>259.9515598178217</v>
+        <v>262.0138729201192</v>
       </c>
       <c r="S36" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
@@ -3516,7 +3516,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3586,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3747,7 +3747,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G41" t="n">
         <v>53.75737228701621</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3817,7 +3817,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3874,13 +3874,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V42" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>82.37314290982852</v>
+        <v>145.050905435271</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3981,7 +3981,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>54.88962870801186</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4057,7 +4057,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4327,7 +4327,7 @@
         <v>30.8</v>
       </c>
       <c r="L2" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="M2" t="n">
         <v>396.55</v>
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="C3" t="n">
-        <v>722.3619790837812</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="D3" t="n">
-        <v>722.3619790837812</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="E3" t="n">
-        <v>376.2285475464957</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="F3" t="n">
-        <v>359.8298342171994</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H3" t="n">
         <v>30.8</v>
@@ -4427,25 +4427,25 @@
         <v>862.6434684666581</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>768.3982803897832</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>762.9863963316884</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>762.7739117254391</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>748.116672138045</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>715.4165277846829</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>695.3531546075237</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.4595557732054</v>
+        <v>1052.914253529113</v>
       </c>
       <c r="C4" t="n">
-        <v>179.4595557732054</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="D4" t="n">
-        <v>282.3059186249661</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="E4" t="n">
-        <v>400.1348228363792</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="F4" t="n">
-        <v>524.4957954283146</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="G4" t="n">
-        <v>677.9023613151999</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4488,13 +4488,13 @@
         <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
         <v>689.8317115219688</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>61.45332037568505</v>
       </c>
       <c r="U4" t="n">
-        <v>68.05025509417312</v>
+        <v>308.0045130139717</v>
       </c>
       <c r="V4" t="n">
-        <v>68.05025509417312</v>
+        <v>506.8259058999176</v>
       </c>
       <c r="W4" t="n">
-        <v>68.05025509417312</v>
+        <v>678.716824159595</v>
       </c>
       <c r="X4" t="n">
-        <v>68.05025509417312</v>
+        <v>829.7476151837885</v>
       </c>
       <c r="Y4" t="n">
-        <v>179.4595557732054</v>
+        <v>941.1569158628208</v>
       </c>
     </row>
     <row r="5">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>411.9499999999999</v>
+        <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>793.0999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>793.1</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>1158.85</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4625,10 +4625,10 @@
         <v>897.189519579215</v>
       </c>
       <c r="F6" t="n">
-        <v>695.3531546075237</v>
+        <v>554.1226081268142</v>
       </c>
       <c r="G6" t="n">
-        <v>366.3233203903244</v>
+        <v>225.0927739096148</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1058.488973253216</v>
+        <v>1247.586867406406</v>
       </c>
       <c r="C7" t="n">
-        <v>1184.490979071652</v>
+        <v>1373.588873224842</v>
       </c>
       <c r="D7" t="n">
-        <v>1297.810123196652</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="E7" t="n">
-        <v>1415.639027408065</v>
+        <v>1540</v>
       </c>
       <c r="F7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>67.02804009978786</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>313.5792327380745</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>512.4006256240204</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>684.2915438836978</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>835.3223349078913</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>946.7316355869236</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
         <v>30.8</v>
@@ -4795,19 +4795,19 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>396.5499999999998</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
-        <v>777.6999999999998</v>
+        <v>411.9499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1158.85</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1158.85</v>
+        <v>793.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="O8" t="n">
         <v>1540</v>
@@ -4822,25 +4822,25 @@
         <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1247.586867406406</v>
+        <v>253.9666383453244</v>
       </c>
       <c r="C10" t="n">
-        <v>1373.588873224842</v>
+        <v>379.9686441637601</v>
       </c>
       <c r="D10" t="n">
-        <v>1486.908017349842</v>
+        <v>493.2877882887602</v>
       </c>
       <c r="E10" t="n">
-        <v>1540</v>
+        <v>611.1166925001733</v>
       </c>
       <c r="F10" t="n">
-        <v>1540</v>
+        <v>735.4776650921087</v>
       </c>
       <c r="G10" t="n">
-        <v>1540</v>
+        <v>888.884230978994</v>
       </c>
       <c r="H10" t="n">
-        <v>1540</v>
+        <v>1058.400816138392</v>
       </c>
       <c r="I10" t="n">
-        <v>1540</v>
+        <v>1279.533695074475</v>
       </c>
       <c r="J10" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>873.3894380368879</v>
+        <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>1024.420229061081</v>
+        <v>30.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1135.829529740114</v>
+        <v>142.2093006790323</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5035,22 +5035,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>618.3311712710653</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L11" t="n">
-        <v>618.3311712710653</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M11" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N11" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5059,25 +5059,25 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X12" t="n">
         <v>204.0388125085078</v>
       </c>
       <c r="Y12" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="13">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5284,10 +5284,10 @@
         <v>1500.287941766591</v>
       </c>
       <c r="O14" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G15" t="n">
         <v>44.72</v>
@@ -5387,13 +5387,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X15" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>444.3729990826727</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C16" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D16" t="n">
         <v>1010.366979583462</v>
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X16" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="17">
@@ -5500,31 +5500,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1243.990904947333</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
         <v>44.72</v>
@@ -5615,22 +5615,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="19">
@@ -5746,19 +5746,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P20" t="n">
         <v>1797.400904947332</v>
@@ -5770,22 +5770,22 @@
         <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
         <v>562.7331275190327</v>
@@ -5801,7 +5801,7 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D21" t="n">
         <v>390.8534315372855</v>
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="K23" t="n">
-        <v>733.1420762183976</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L23" t="n">
-        <v>733.1420762183976</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M23" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1129.18</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6083,10 +6083,10 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S24" t="n">
-        <v>466.2983195781991</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T24" t="n">
         <v>410.3813850150538</v>
@@ -6114,16 +6114,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E25" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F25" t="n">
         <v>1153.55685638681</v>
@@ -6168,22 +6168,22 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="26">
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>626.8200754279619</v>
+        <v>632.3798821093615</v>
       </c>
       <c r="C26" t="n">
-        <v>494.0174711421095</v>
+        <v>499.577277823509</v>
       </c>
       <c r="D26" t="n">
-        <v>400.7455966574127</v>
+        <v>406.3054033388123</v>
       </c>
       <c r="E26" t="n">
-        <v>313.5099505898686</v>
+        <v>319.0697572712681</v>
       </c>
       <c r="F26" t="n">
-        <v>225.7426488646041</v>
+        <v>231.3024555460037</v>
       </c>
       <c r="G26" t="n">
         <v>144.6788471752802</v>
@@ -6217,52 +6217,52 @@
         <v>53.76</v>
       </c>
       <c r="J26" t="n">
-        <v>233.3708514962945</v>
+        <v>445.0691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>233.3708514962945</v>
+        <v>445.0691130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>898.6508514962944</v>
+        <v>460.0517564436332</v>
       </c>
       <c r="M26" t="n">
-        <v>1409.499680225229</v>
+        <v>970.9005851725682</v>
       </c>
       <c r="N26" t="n">
-        <v>2022.719999999993</v>
+        <v>1584.120904947331</v>
       </c>
       <c r="O26" t="n">
-        <v>2022.719999999993</v>
+        <v>1584.120904947331</v>
       </c>
       <c r="P26" t="n">
-        <v>2688</v>
+        <v>2249.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>2688</v>
       </c>
       <c r="R26" t="n">
-        <v>2688</v>
+        <v>2688.000000000011</v>
       </c>
       <c r="S26" t="n">
-        <v>2509.365487068361</v>
+        <v>2514.92529374976</v>
       </c>
       <c r="T26" t="n">
-        <v>2237.976010574862</v>
+        <v>2243.535817256261</v>
       </c>
       <c r="U26" t="n">
-        <v>1903.409044364144</v>
+        <v>1908.968851045543</v>
       </c>
       <c r="V26" t="n">
-        <v>1588.408009852201</v>
+        <v>1593.9678165336</v>
       </c>
       <c r="W26" t="n">
-        <v>1264.798438154274</v>
+        <v>1270.358244835673</v>
       </c>
       <c r="X26" t="n">
-        <v>987.7460811232962</v>
+        <v>993.3058878046958</v>
       </c>
       <c r="Y26" t="n">
-        <v>792.4759471002594</v>
+        <v>798.035753781659</v>
       </c>
     </row>
     <row r="27">
@@ -6293,28 +6293,28 @@
         <v>53.76</v>
       </c>
       <c r="I27" t="n">
-        <v>53.76</v>
+        <v>59.29119898333113</v>
       </c>
       <c r="J27" t="n">
-        <v>177.7165201752989</v>
+        <v>183.2477191586301</v>
       </c>
       <c r="K27" t="n">
-        <v>366.9093362696823</v>
+        <v>372.4405352530135</v>
       </c>
       <c r="L27" t="n">
-        <v>638.2597978648824</v>
+        <v>643.7909968482136</v>
       </c>
       <c r="M27" t="n">
-        <v>724.3403396077417</v>
+        <v>729.8715385910729</v>
       </c>
       <c r="N27" t="n">
-        <v>857.62062421531</v>
+        <v>863.1518231986412</v>
       </c>
       <c r="O27" t="n">
-        <v>1096.663075899029</v>
+        <v>1102.19427488236</v>
       </c>
       <c r="P27" t="n">
-        <v>1209.192420368536</v>
+        <v>1214.723619351867</v>
       </c>
       <c r="Q27" t="n">
         <v>1214.723619351867</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>626.8200754280206</v>
+        <v>626.8200754280788</v>
       </c>
       <c r="C29" t="n">
-        <v>494.0174711421681</v>
+        <v>494.0174711422263</v>
       </c>
       <c r="D29" t="n">
-        <v>400.7455966574714</v>
+        <v>400.7455966575296</v>
       </c>
       <c r="E29" t="n">
-        <v>313.5099505899273</v>
+        <v>313.5099505899855</v>
       </c>
       <c r="F29" t="n">
-        <v>225.7426488646628</v>
+        <v>225.742648864721</v>
       </c>
       <c r="G29" t="n">
-        <v>139.1190404939393</v>
+        <v>139.1190404939975</v>
       </c>
       <c r="H29" t="n">
         <v>53.76</v>
@@ -6478,28 +6478,28 @@
         <v>2688</v>
       </c>
       <c r="R29" t="n">
-        <v>2688.000000000059</v>
+        <v>2688.000000000117</v>
       </c>
       <c r="S29" t="n">
-        <v>2509.365487068419</v>
+        <v>2509.365487068478</v>
       </c>
       <c r="T29" t="n">
-        <v>2237.976010574921</v>
+        <v>2237.976010574979</v>
       </c>
       <c r="U29" t="n">
-        <v>1903.409044364203</v>
+        <v>1903.409044364261</v>
       </c>
       <c r="V29" t="n">
-        <v>1588.408009852259</v>
+        <v>1588.408009852317</v>
       </c>
       <c r="W29" t="n">
-        <v>1264.798438154332</v>
+        <v>1264.798438154391</v>
       </c>
       <c r="X29" t="n">
-        <v>987.7460811233549</v>
+        <v>987.7460811234131</v>
       </c>
       <c r="Y29" t="n">
-        <v>792.4759471003181</v>
+        <v>792.4759471003763</v>
       </c>
     </row>
     <row r="30">
@@ -6536,25 +6536,25 @@
         <v>177.7165201752989</v>
       </c>
       <c r="K30" t="n">
-        <v>372.4405352530135</v>
+        <v>366.9093362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>643.7909968482136</v>
+        <v>638.2597978648824</v>
       </c>
       <c r="M30" t="n">
-        <v>729.8715385910729</v>
+        <v>724.3403396077417</v>
       </c>
       <c r="N30" t="n">
-        <v>863.1518231986412</v>
+        <v>857.62062421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1102.19427488236</v>
+        <v>1096.663075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1214.723619351867</v>
+        <v>1209.192420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351832</v>
       </c>
       <c r="R30" t="n">
         <v>983.1339251171403</v>
@@ -6621,19 +6621,19 @@
         <v>1431.431843630702</v>
       </c>
       <c r="M31" t="n">
-        <v>1420.343639499571</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="N31" t="n">
-        <v>1164.601139225142</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="O31" t="n">
-        <v>838.8985492463389</v>
+        <v>1105.729253651899</v>
       </c>
       <c r="P31" t="n">
-        <v>465.7188549753515</v>
+        <v>878.4482771785345</v>
       </c>
       <c r="Q31" t="n">
-        <v>53.76</v>
+        <v>466.4894222031829</v>
       </c>
       <c r="R31" t="n">
         <v>53.76</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>626.8200754279651</v>
+        <v>632.3798821093615</v>
       </c>
       <c r="C32" t="n">
-        <v>494.0174711421126</v>
+        <v>499.577277823509</v>
       </c>
       <c r="D32" t="n">
-        <v>400.7455966574159</v>
+        <v>406.3054033388123</v>
       </c>
       <c r="E32" t="n">
-        <v>313.5099505898718</v>
+        <v>319.0697572712681</v>
       </c>
       <c r="F32" t="n">
-        <v>225.7426488646073</v>
+        <v>231.3024555460037</v>
       </c>
       <c r="G32" t="n">
-        <v>139.1190404938838</v>
+        <v>144.6788471752802</v>
       </c>
       <c r="H32" t="n">
         <v>53.76</v>
@@ -6691,52 +6691,52 @@
         <v>53.76</v>
       </c>
       <c r="J32" t="n">
-        <v>53.76</v>
+        <v>445.0691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>460.0517564436341</v>
+        <v>1110.349113037656</v>
       </c>
       <c r="L32" t="n">
-        <v>460.0517564436341</v>
+        <v>1775.629113037656</v>
       </c>
       <c r="M32" t="n">
-        <v>970.9005851725691</v>
+        <v>2286.47794176659</v>
       </c>
       <c r="N32" t="n">
-        <v>1584.120904947332</v>
+        <v>2286.47794176659</v>
       </c>
       <c r="O32" t="n">
-        <v>2249.400904947332</v>
+        <v>2688</v>
       </c>
       <c r="P32" t="n">
-        <v>2249.400904947332</v>
+        <v>2688</v>
       </c>
       <c r="Q32" t="n">
         <v>2688</v>
       </c>
       <c r="R32" t="n">
-        <v>2688.000000000003</v>
+        <v>2688</v>
       </c>
       <c r="S32" t="n">
-        <v>2509.365487068364</v>
+        <v>2509.365487068361</v>
       </c>
       <c r="T32" t="n">
-        <v>2237.976010574865</v>
+        <v>2237.976010574862</v>
       </c>
       <c r="U32" t="n">
-        <v>1903.409044364147</v>
+        <v>1903.409044364144</v>
       </c>
       <c r="V32" t="n">
-        <v>1588.408009852204</v>
+        <v>1588.408009852201</v>
       </c>
       <c r="W32" t="n">
-        <v>1264.798438154277</v>
+        <v>1264.798438154274</v>
       </c>
       <c r="X32" t="n">
-        <v>987.7460811232994</v>
+        <v>987.7460811232962</v>
       </c>
       <c r="Y32" t="n">
-        <v>792.4759471002626</v>
+        <v>798.035753781659</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>196.4403656206666</v>
+        <v>196.4403656204576</v>
       </c>
       <c r="C33" t="n">
-        <v>152.9051005241824</v>
+        <v>152.9051005239735</v>
       </c>
       <c r="D33" t="n">
-        <v>122.6650127487252</v>
+        <v>122.6650127485162</v>
       </c>
       <c r="E33" t="n">
-        <v>97.74370242356093</v>
+        <v>97.74370242335198</v>
       </c>
       <c r="F33" t="n">
-        <v>75.88891218328128</v>
+        <v>75.88891218307232</v>
       </c>
       <c r="G33" t="n">
-        <v>68.07119917820316</v>
+        <v>68.0711991779942</v>
       </c>
       <c r="H33" t="n">
-        <v>53.76</v>
+        <v>53.75999999979103</v>
       </c>
       <c r="I33" t="n">
-        <v>59.29119898333113</v>
+        <v>59.2911989831008</v>
       </c>
       <c r="J33" t="n">
-        <v>183.2477191586301</v>
+        <v>183.2477191583997</v>
       </c>
       <c r="K33" t="n">
-        <v>372.4405352530135</v>
+        <v>372.4405352527831</v>
       </c>
       <c r="L33" t="n">
-        <v>643.7909968482136</v>
+        <v>643.7909968479833</v>
       </c>
       <c r="M33" t="n">
-        <v>729.8715385910729</v>
+        <v>729.8715385908425</v>
       </c>
       <c r="N33" t="n">
-        <v>863.1518231986412</v>
+        <v>863.1518231984109</v>
       </c>
       <c r="O33" t="n">
-        <v>1102.19427488236</v>
+        <v>1102.19427488213</v>
       </c>
       <c r="P33" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351636</v>
       </c>
       <c r="Q33" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351636</v>
       </c>
       <c r="R33" t="n">
-        <v>983.1339251171403</v>
+        <v>983.1339251169313</v>
       </c>
       <c r="S33" t="n">
-        <v>833.0692786882399</v>
+        <v>833.069278688031</v>
       </c>
       <c r="T33" t="n">
-        <v>744.8291118018624</v>
+        <v>744.8291118016534</v>
       </c>
       <c r="U33" t="n">
-        <v>661.7883443673303</v>
+        <v>661.7883443671213</v>
       </c>
       <c r="V33" t="n">
-        <v>564.3028219516534</v>
+        <v>564.3028219514445</v>
       </c>
       <c r="W33" t="n">
-        <v>448.7743947700085</v>
+        <v>448.7743947697995</v>
       </c>
       <c r="X33" t="n">
-        <v>345.8827387645665</v>
+        <v>345.8827387643576</v>
       </c>
       <c r="Y33" t="n">
-        <v>263.6692107179662</v>
+        <v>263.6692107177572</v>
       </c>
     </row>
     <row r="34">
@@ -6858,19 +6858,19 @@
         <v>1431.431843630702</v>
       </c>
       <c r="M34" t="n">
-        <v>1226.753448274591</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="N34" t="n">
-        <v>971.0109480001622</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="O34" t="n">
-        <v>645.3083580213593</v>
+        <v>1105.729253651899</v>
       </c>
       <c r="P34" t="n">
-        <v>272.1286637503719</v>
+        <v>878.4482771785345</v>
       </c>
       <c r="Q34" t="n">
-        <v>53.76</v>
+        <v>466.4894222031829</v>
       </c>
       <c r="R34" t="n">
         <v>53.76</v>
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M35" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>937.5750872192207</v>
+        <v>935.4919426714454</v>
       </c>
       <c r="S36" t="n">
-        <v>466.2983195781991</v>
+        <v>817.7505285657774</v>
       </c>
       <c r="T36" t="n">
-        <v>410.3813850150538</v>
+        <v>761.8335940026321</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>711.1160588913324</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5015598113094</v>
+        <v>645.9537687988877</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>562.7485739404751</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="37">
@@ -7116,13 +7116,13 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
         <v>644.3484002705077</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
         <v>44.72</v>
@@ -7168,19 +7168,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>618.3311712710652</v>
+        <v>575.7700000000002</v>
       </c>
       <c r="L38" t="n">
-        <v>1171.741171271065</v>
+        <v>1129.18</v>
       </c>
       <c r="M38" t="n">
+        <v>1129.18</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1129.18</v>
+      </c>
+      <c r="O38" t="n">
         <v>1682.59</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1682.59</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2236</v>
       </c>
       <c r="P38" t="n">
         <v>2236</v>
@@ -7192,25 +7192,25 @@
         <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G39" t="n">
         <v>44.72</v>
@@ -7274,22 +7274,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
         <v>1860.696627021627</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
         <v>157.615990899539</v>
@@ -7402,25 +7402,25 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>137.1709049473328</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>690.5809049473327</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M41" t="n">
-        <v>690.5809049473327</v>
+        <v>1682.59</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7429,25 +7429,25 @@
         <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
         <v>44.72</v>
@@ -7517,16 +7517,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W42" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
         <v>213.0600603015712</v>
@@ -7639,16 +7639,16 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L44" t="n">
-        <v>1542.849113037656</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
         <v>1797.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
         <v>44.72</v>
@@ -7745,25 +7745,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7970,10 +7970,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>913.7065720867618</v>
       </c>
       <c r="N2" t="n">
         <v>862.2489580698352</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N5" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>455.2478695740924</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>404.4874506895347</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>385</v>
@@ -8450,10 +8450,10 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>455.2478695740924</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
@@ -8678,7 +8678,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>184.1434931650601</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8690,13 +8690,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8927,13 +8927,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,13 +9389,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
@@ -9404,7 +9404,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121691</v>
       </c>
       <c r="K23" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>216.4681087666</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>672</v>
+        <v>15.13398323836111</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9878,10 +9878,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>672.287060040689</v>
+        <v>672.2870600406825</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10112,7 +10112,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>742.2478695740925</v>
+        <v>742.2478695740924</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>410.3957135794284</v>
+        <v>672</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>742.2478695740928</v>
+        <v>475.8257061734961</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,16 +10583,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,13 +10811,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>184.14349316506</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>477.2489580698352</v>
@@ -10826,7 +10826,7 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
         <v>172.8226843274854</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,19 +11282,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>734.3719802008218</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.5911706460559</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22712,7 +22712,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.591170646055843</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5.504208614585579</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.504208614574424</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>5.504208614527485</v>
+        <v>5.50420861446986</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24836,22 +24836,22 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>191.6542893127299</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>144.4397306196462</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>408.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>44.37347970285543</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5.50420861458241</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24951,7 +24951,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>5.504208614585508</v>
       </c>
     </row>
     <row r="33">
@@ -25073,22 +25073,22 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>144.4397306196462</v>
       </c>
       <c r="Q34" t="n">
-        <v>191.6542893127298</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>408.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>44.37347970285543</v>
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9486324.84866683</v>
+        <v>9486324.848666834</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11356216.24639805</v>
+        <v>11356216.24639806</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12300749.0266475</v>
+        <v>12300749.02664751</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13245281.80689695</v>
+        <v>13245281.80689696</v>
       </c>
     </row>
     <row r="16">
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1259338.852237089</v>
+        <v>1259338.85223709</v>
       </c>
       <c r="C2" t="n">
-        <v>1259338.852237089</v>
+        <v>1259338.85223709</v>
       </c>
       <c r="D2" t="n">
         <v>1259338.852237089</v>
@@ -26281,25 +26281,25 @@
         <v>1259377.040332595</v>
       </c>
       <c r="F2" t="n">
-        <v>1259377.040332596</v>
+        <v>1259377.040332595</v>
       </c>
       <c r="G2" t="n">
         <v>1259377.040332595</v>
       </c>
       <c r="H2" t="n">
-        <v>1259377.040332595</v>
+        <v>1259377.040332596</v>
       </c>
       <c r="I2" t="n">
         <v>1259377.040332595</v>
       </c>
       <c r="J2" t="n">
-        <v>1240934.644723166</v>
+        <v>1240934.644723167</v>
       </c>
       <c r="K2" t="n">
-        <v>1240934.644723171</v>
+        <v>1240934.644723175</v>
       </c>
       <c r="L2" t="n">
-        <v>1240934.644723166</v>
+        <v>1240934.644723165</v>
       </c>
       <c r="M2" t="n">
         <v>1259377.040332595</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.3728533789</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>509242.089049618</v>
+        <v>511130.7051621599</v>
       </c>
       <c r="K4" t="n">
-        <v>507410.094517139</v>
+        <v>509298.710629683</v>
       </c>
       <c r="L4" t="n">
-        <v>505575.4970691491</v>
+        <v>507464.1131816903</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495869.1273375802</v>
+        <v>494353.2716492651</v>
       </c>
       <c r="C6" t="n">
-        <v>633447.1074713945</v>
+        <v>631931.2517830794</v>
       </c>
       <c r="D6" t="n">
-        <v>635507.8793837104</v>
+        <v>633992.0236953943</v>
       </c>
       <c r="E6" t="n">
-        <v>311623.6371060599</v>
+        <v>309881.7872929523</v>
       </c>
       <c r="F6" t="n">
-        <v>654814.5324515646</v>
+        <v>653072.6826384562</v>
       </c>
       <c r="G6" t="n">
-        <v>656760.1089197494</v>
+        <v>655018.2591066419</v>
       </c>
       <c r="H6" t="n">
-        <v>658708.3857370509</v>
+        <v>656966.5359239437</v>
       </c>
       <c r="I6" t="n">
-        <v>660659.3823804111</v>
+        <v>658917.5325673035</v>
       </c>
       <c r="J6" t="n">
-        <v>234405.0136735482</v>
+        <v>232516.3975610068</v>
       </c>
       <c r="K6" t="n">
-        <v>665933.0082060316</v>
+        <v>664044.3920934923</v>
       </c>
       <c r="L6" t="n">
-        <v>667767.6056540172</v>
+        <v>665878.989541475</v>
       </c>
       <c r="M6" t="n">
-        <v>621418.9657904939</v>
+        <v>619677.1159773866</v>
       </c>
       <c r="N6" t="n">
-        <v>670455.8628253478</v>
+        <v>668714.0130122399</v>
       </c>
       <c r="O6" t="n">
-        <v>418023.6020830863</v>
+        <v>416281.7522699785</v>
       </c>
       <c r="P6" t="n">
-        <v>674394.2049340963</v>
+        <v>672652.3551209888</v>
       </c>
     </row>
   </sheetData>
@@ -26993,13 +26993,13 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -27082,13 +27082,13 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -27097,7 +27097,7 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>498</v>
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>323.4015161418735</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27563,7 +27563,7 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>373.2612637685052</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>389.421433057334</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
+        <v>240.9875163806871</v>
+      </c>
+      <c r="U4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
-      </c>
-      <c r="U4" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27761,13 +27761,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>139.8182410159025</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27837,10 +27837,10 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>334.6091701401468</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>245.04387284153</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>246.6185464050333</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28074,25 +28074,25 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>334.6091701401468</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>186.8870003396018</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28226,7 +28226,7 @@
         <v>350</v>
       </c>
       <c r="C12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28289,10 +28289,10 @@
         <v>350</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
     </row>
     <row r="13">
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28472,10 +28472,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>332.1680871864211</v>
@@ -28523,7 +28523,7 @@
         <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X15" t="n">
         <v>350</v>
@@ -28545,7 +28545,7 @@
         <v>350</v>
       </c>
       <c r="D16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,7 +28700,7 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -28709,7 +28709,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>276.9584798124343</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>325.7395358750273</v>
@@ -28751,7 +28751,7 @@
         <v>350</v>
       </c>
       <c r="T18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>350</v>
@@ -28906,7 +28906,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28924,7 +28924,7 @@
         <v>350</v>
       </c>
       <c r="Y20" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
     </row>
     <row r="21">
@@ -28937,10 +28937,10 @@
         <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
       <c r="D21" t="n">
-        <v>277.9320215941727</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -29113,7 +29113,7 @@
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29219,13 +29219,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S24" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>350</v>
@@ -29262,7 +29262,7 @@
         <v>350</v>
       </c>
       <c r="F25" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G25" t="n">
         <v>350</v>
@@ -29304,7 +29304,7 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283059</v>
       </c>
       <c r="S26" t="n">
         <v>318</v>
@@ -29429,7 +29429,7 @@
         <v>318</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>222.713455571481</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>178.6663347706119</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
         <v>318</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988283537</v>
+        <v>250.8785988284125</v>
       </c>
       <c r="S29" t="n">
         <v>318</v>
@@ -29672,7 +29672,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>5.587069680132458</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -29690,10 +29690,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>178.6663347705768</v>
       </c>
       <c r="R30" t="n">
-        <v>318</v>
+        <v>318.0000000000346</v>
       </c>
       <c r="S30" t="n">
         <v>318</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>250.8785988282976</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>318</v>
@@ -29903,7 +29903,7 @@
         <v>318</v>
       </c>
       <c r="I33" t="n">
-        <v>222.713455571481</v>
+        <v>222.7134555714594</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29930,7 +29930,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>318</v>
+        <v>318.0000000000212</v>
       </c>
       <c r="S33" t="n">
         <v>318</v>
@@ -30125,7 +30125,7 @@
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30167,10 +30167,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>287.3222374745576</v>
+        <v>285.25992437226</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30261,7 +30261,7 @@
         <v>350</v>
       </c>
       <c r="W37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X37" t="n">
         <v>350</v>
@@ -30295,7 +30295,7 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30365,13 +30365,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>255.7338705714974</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>332.1680871864211</v>
@@ -30410,7 +30410,7 @@
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30526,7 +30526,7 @@
         <v>350</v>
       </c>
       <c r="F41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G41" t="n">
         <v>350</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30596,7 +30596,7 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -30653,13 +30653,13 @@
         <v>350</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30760,7 +30760,7 @@
         <v>350</v>
       </c>
       <c r="E44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F44" t="n">
         <v>350</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30836,7 +30836,7 @@
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30881,7 +30881,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -34749,10 +34749,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="N2" t="n">
         <v>385</v>
@@ -34877,34 +34877,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8852150017785</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>30.96294987442934</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="N5" t="n">
         <v>385</v>
-      </c>
-      <c r="L5" t="n">
-        <v>385</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>369.4444444444443</v>
       </c>
       <c r="O5" t="n">
         <v>385</v>
@@ -35123,10 +35123,10 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>53.62826530319025</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>36.59397989877561</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>369.4444444444443</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>385</v>
@@ -35229,10 +35229,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35360,25 +35360,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>53.62826530319025</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>151.618051503694</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,7 +35457,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>184.1434931650601</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -35469,13 +35469,13 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35706,13 +35706,13 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>559</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,7 +35831,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E16" t="n">
         <v>69.01909516304346</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36168,13 +36168,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>257.1230221309868</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
@@ -36183,7 +36183,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612659</v>
       </c>
       <c r="K23" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -36414,16 +36414,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
         <v>559</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36548,7 +36548,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G25" t="n">
         <v>104.95612715847</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>181.4251025215096</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>672</v>
+        <v>15.13398323836111</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36657,13 +36657,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>672.0000000000075</v>
+        <v>672.000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.14835189617794e-11</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.587069680132455</v>
       </c>
       <c r="J27" t="n">
         <v>125.2086062376757</v>
@@ -36739,7 +36739,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.587069680132347</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36891,7 +36891,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>672.0000000000001</v>
+        <v>672</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36900,7 +36900,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.925495784278169e-11</v>
+        <v>1.180505749270922e-10</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -36958,7 +36958,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>196.6909243209238</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
         <v>274.091375348687</v>
@@ -36976,7 +36976,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.587069680097208</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,31 +37113,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>410.3957135794284</v>
+        <v>672</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>672.0000000000003</v>
+        <v>405.5778365994036</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.215385309298231e-12</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>5.587069680132455</v>
+        <v>5.587069680110873</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37353,7 +37353,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>184.1434931650601</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -37362,16 +37362,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>559</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37547,7 +37547,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X37" t="n">
         <v>102.5563545698924</v>
@@ -37590,13 +37590,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>184.14349316506</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
+        <v>136.375834564038</v>
+      </c>
+      <c r="M44" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N44" t="n">
         <v>559</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>257.1230221309866</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
